--- a/data_lake/reporte_cordoba_mes/dt=2026-09-20/CORDOBA_SEP26.xlsx
+++ b/data_lake/reporte_cordoba_mes/dt=2026-09-20/CORDOBA_SEP26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E211B4-E27B-4242-8460-6633681198B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCC7CF3-F5DC-43C2-A31D-AB04F4A07ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{5F8F14AC-D557-4126-B18A-7A2C1E69122F}"/>
   </bookViews>
@@ -10014,7 +10014,7 @@
                   <c:v>11.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1</c:v>
+                  <c:v>220.79999999999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>-1</c:v>
@@ -19975,7 +19975,9 @@
       <c r="V3" s="25">
         <v>0</v>
       </c>
-      <c r="W3" s="25"/>
+      <c r="W3" s="25">
+        <v>15.7</v>
+      </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="25"/>
       <c r="Z3" s="25"/>
@@ -19990,7 +19992,7 @@
       <c r="AI3" s="34"/>
       <c r="AJ3" s="36">
         <f>SUM(E3:AI3)</f>
-        <v>52.500000000000007</v>
+        <v>68.2</v>
       </c>
       <c r="AK3" s="30">
         <v>27.817857142857147</v>
@@ -20063,7 +20065,9 @@
       <c r="V4" s="25">
         <v>0</v>
       </c>
-      <c r="W4" s="25"/>
+      <c r="W4" s="25">
+        <v>21</v>
+      </c>
       <c r="X4" s="25"/>
       <c r="Y4" s="25"/>
       <c r="Z4" s="25"/>
@@ -20078,7 +20082,7 @@
       <c r="AI4" s="34"/>
       <c r="AJ4" s="36">
         <f t="shared" ref="AJ4:AJ17" si="0">SUM(E4:AI4)</f>
-        <v>33.200000000000003</v>
+        <v>54.2</v>
       </c>
       <c r="AK4" s="30">
         <v>47.628571428571419</v>
@@ -20151,7 +20155,9 @@
       <c r="V5" s="25">
         <v>0</v>
       </c>
-      <c r="W5" s="25"/>
+      <c r="W5" s="25">
+        <v>59.8</v>
+      </c>
       <c r="X5" s="25"/>
       <c r="Y5" s="25"/>
       <c r="Z5" s="25"/>
@@ -20166,7 +20172,7 @@
       <c r="AI5" s="34"/>
       <c r="AJ5" s="36">
         <f t="shared" si="0"/>
-        <v>216.3</v>
+        <v>276.10000000000002</v>
       </c>
       <c r="AK5" s="30">
         <v>40.986206896551728</v>
@@ -20239,7 +20245,9 @@
       <c r="V6" s="25">
         <v>0</v>
       </c>
-      <c r="W6" s="25"/>
+      <c r="W6" s="25">
+        <v>0</v>
+      </c>
       <c r="X6" s="25"/>
       <c r="Y6" s="25"/>
       <c r="Z6" s="25"/>
@@ -20431,7 +20439,9 @@
       <c r="V9" s="25">
         <v>0</v>
       </c>
-      <c r="W9" s="25"/>
+      <c r="W9" s="25">
+        <v>0</v>
+      </c>
       <c r="X9" s="25"/>
       <c r="Y9" s="25"/>
       <c r="Z9" s="25"/>
@@ -20566,8 +20576,12 @@
       <c r="U11" s="25">
         <v>0</v>
       </c>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
+      <c r="V11" s="25">
+        <v>0</v>
+      </c>
+      <c r="W11" s="25">
+        <v>27.5</v>
+      </c>
       <c r="X11" s="25"/>
       <c r="Y11" s="25"/>
       <c r="Z11" s="25"/>
@@ -20582,7 +20596,7 @@
       <c r="AI11" s="34"/>
       <c r="AJ11" s="36">
         <f t="shared" si="0"/>
-        <v>17.099999999999998</v>
+        <v>44.599999999999994</v>
       </c>
       <c r="AK11" s="30">
         <v>19.188461538461539</v>
@@ -20655,7 +20669,9 @@
       <c r="V12" s="25">
         <v>11.5</v>
       </c>
-      <c r="W12" s="25"/>
+      <c r="W12" s="25">
+        <v>3.5</v>
+      </c>
       <c r="X12" s="25"/>
       <c r="Y12" s="25"/>
       <c r="Z12" s="25"/>
@@ -20670,7 +20686,7 @@
       <c r="AI12" s="34"/>
       <c r="AJ12" s="36">
         <f t="shared" si="0"/>
-        <v>73.5</v>
+        <v>77</v>
       </c>
       <c r="AK12" s="30">
         <v>34.724137931034484</v>
@@ -20743,7 +20759,9 @@
       <c r="V13" s="25">
         <v>0</v>
       </c>
-      <c r="W13" s="25"/>
+      <c r="W13" s="25">
+        <v>46</v>
+      </c>
       <c r="X13" s="25"/>
       <c r="Y13" s="25"/>
       <c r="Z13" s="25"/>
@@ -20758,7 +20776,7 @@
       <c r="AI13" s="34"/>
       <c r="AJ13" s="36">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="AK13" s="30"/>
     </row>
@@ -20829,7 +20847,9 @@
       <c r="V14" s="25">
         <v>0</v>
       </c>
-      <c r="W14" s="25"/>
+      <c r="W14" s="25">
+        <v>30.1</v>
+      </c>
       <c r="X14" s="25"/>
       <c r="Y14" s="25"/>
       <c r="Z14" s="25"/>
@@ -20844,7 +20864,7 @@
       <c r="AI14" s="34"/>
       <c r="AJ14" s="36">
         <f>SUM(E14:AI14)</f>
-        <v>38.800000000000004</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="AK14" s="30">
         <v>36.1</v>
@@ -20917,7 +20937,9 @@
       <c r="V15" s="25">
         <v>0</v>
       </c>
-      <c r="W15" s="25"/>
+      <c r="W15" s="25">
+        <v>17.2</v>
+      </c>
       <c r="X15" s="25"/>
       <c r="Y15" s="25"/>
       <c r="Z15" s="25"/>
@@ -20932,7 +20954,7 @@
       <c r="AI15" s="34"/>
       <c r="AJ15" s="36">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>29.2</v>
       </c>
       <c r="AK15" s="30">
         <v>60.46</v>
@@ -21114,7 +21136,7 @@
       </c>
       <c r="W19" s="26">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>220.79999999999998</v>
       </c>
       <c r="X19" s="26">
         <f t="shared" si="1"/>
